--- a/ig/mp-python/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/mp-python/CodeSystem-terminologie-cim11-mms.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-31T16:47:49+00:00</t>
+    <t>2024-04-01T14:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
